--- a/aa-docs/1_个人记录/编年记录.xlsx
+++ b/aa-docs/1_个人记录/编年记录.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="11055"/>
+    <workbookView windowWidth="29868" windowHeight="13500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,19 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>生平记录</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="华文楷体"/>
+        <charset val="134"/>
+      </rPr>
       <t>本记录宗旨:</t>
     </r>
     <r>
@@ -123,15 +130,19 @@
     <t>2024.10</t>
   </si>
   <si>
-    <t>1、从杭回老家，看小宝和家人，开封办小宝百天宴。
+    <t xml:space="preserve">1、从杭回老家，看小宝和家人，开封办小宝百天宴。
 2、爸妈去安徽种麦。
 3、开启中海油项目，该项目使我接触到了一种新的开发架构设计。
-4、继续已经开始的技术学习（k8s）。</t>
+4、继续已经开始的技术学习（k8s）。
+</t>
   </si>
   <si>
     <t>1、技术逐个突破（k8s）。
 2、2025年初换工作，工资目标3万，最少2.5万，15薪。
 3、把自己学习的体系换成中海油的架构体系。</t>
+  </si>
+  <si>
+    <t>1、妈妈和乐儿带着小宝来杭州，产假结束。</t>
   </si>
 </sst>
 </file>
@@ -827,7 +838,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -837,9 +848,6 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -862,9 +870,6 @@
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1179,234 +1184,236 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="12.0530973451327" style="1" customWidth="1"/>
-    <col min="2" max="2" width="46.4159292035398" customWidth="1"/>
-    <col min="3" max="3" width="22.0088495575221" customWidth="1"/>
-    <col min="4" max="4" width="36.6637168141593" customWidth="1"/>
-    <col min="5" max="5" width="26.3982300884956" customWidth="1"/>
+    <col min="1" max="1" width="12.0555555555556" style="1" customWidth="1"/>
+    <col min="2" max="2" width="46.4166666666667" customWidth="1"/>
+    <col min="3" max="3" width="22.0092592592593" customWidth="1"/>
+    <col min="4" max="4" width="36.6666666666667" customWidth="1"/>
+    <col min="5" max="5" width="26.3981481481481" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.75" spans="1:5">
+    <row r="1" ht="28.2" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="4"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="3"/>
     </row>
     <row r="2" ht="68" customHeight="1" spans="1:5">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="7"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="6"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="10">
+      <c r="A4" s="9">
         <v>2014</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="10">
+      <c r="A5" s="9">
         <v>2015</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="10">
+      <c r="A6" s="9">
         <v>2016</v>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="10">
+      <c r="A7" s="9">
         <v>2017</v>
       </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="10">
+      <c r="A8" s="9">
         <v>2018</v>
       </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="10">
+      <c r="A9" s="9">
         <v>2019</v>
       </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="10">
+      <c r="A10" s="9">
         <v>2020</v>
       </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="10">
+      <c r="A11" s="9">
         <v>2021</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="10">
+      <c r="A12" s="9">
         <v>2022</v>
       </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="10">
+      <c r="A13" s="9">
         <v>2023.11</v>
       </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="10"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="10"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-    </row>
-    <row r="16" ht="39" spans="1:5">
-      <c r="A16" s="12" t="s">
+      <c r="A15" s="9"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+    </row>
+    <row r="16" ht="38.4" spans="1:5">
+      <c r="A16" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
     </row>
     <row r="17" ht="135" customHeight="1" spans="1:5">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-    </row>
-    <row r="18" ht="39" spans="1:5">
-      <c r="A18" s="12" t="s">
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+    </row>
+    <row r="18" ht="48" spans="1:5">
+      <c r="A18" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
     </row>
     <row r="19" ht="28" customHeight="1" spans="1:5">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
     </row>
     <row r="20" ht="32" customHeight="1" spans="1:5">
-      <c r="A20" s="12" t="s">
+      <c r="A20" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11" t="s">
+      <c r="C20" s="10"/>
+      <c r="D20" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="11"/>
+      <c r="E20" s="10"/>
     </row>
     <row r="21" ht="40.5" customHeight="1" spans="1:5">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11" t="s">
+      <c r="C21" s="10"/>
+      <c r="D21" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="11"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="10">
+      <c r="E21" s="10"/>
+    </row>
+    <row r="22" ht="68" customHeight="1" spans="1:5">
+      <c r="A22" s="9">
         <v>2024.11</v>
       </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
+      <c r="B22" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1423,7 +1430,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1435,7 +1442,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
